--- a/Daily Sales Forecasting Methodology/Historical festive feature_yash.xlsx
+++ b/Daily Sales Forecasting Methodology/Historical festive feature_yash.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\G0004878\Desktop\TFT_Data\Daily_forecasting_model\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\G0004878\Desktop\TFT_Data\Temporal-Fusion-Transformers-Material\Daily Sales Forecasting Methodology\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="51">
   <si>
     <t>Date</t>
   </si>
@@ -159,6 +159,27 @@
   </si>
   <si>
     <t>ONAM</t>
+  </si>
+  <si>
+    <t>C</t>
+  </si>
+  <si>
+    <t>C+1</t>
+  </si>
+  <si>
+    <t>C+2</t>
+  </si>
+  <si>
+    <t>C+3</t>
+  </si>
+  <si>
+    <t>C+4</t>
+  </si>
+  <si>
+    <t>C+5</t>
+  </si>
+  <si>
+    <t>C+6</t>
   </si>
 </sst>
 </file>
@@ -479,7 +500,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AR377"/>
+  <dimension ref="A1:AY377"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="10.54296875" customWidth="1"/>
@@ -500,7 +521,7 @@
     <col min="39" max="44" width="8.6328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:44" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:51" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -633,8 +654,29 @@
       <c r="AR1" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="2" spans="1:44" x14ac:dyDescent="0.35">
+      <c r="AS1" t="s">
+        <v>44</v>
+      </c>
+      <c r="AT1" t="s">
+        <v>45</v>
+      </c>
+      <c r="AU1" t="s">
+        <v>46</v>
+      </c>
+      <c r="AV1" t="s">
+        <v>47</v>
+      </c>
+      <c r="AW1" t="s">
+        <v>48</v>
+      </c>
+      <c r="AX1" t="s">
+        <v>49</v>
+      </c>
+      <c r="AY1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="2" spans="1:51" x14ac:dyDescent="0.35">
       <c r="A2" s="1">
         <v>45170</v>
       </c>
@@ -646,7 +688,7 @@
       <c r="G2" s="1"/>
       <c r="H2" s="1"/>
     </row>
-    <row r="3" spans="1:44" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:51" x14ac:dyDescent="0.35">
       <c r="A3" s="1">
         <v>45171</v>
       </c>
@@ -658,7 +700,7 @@
       <c r="G3" s="1"/>
       <c r="H3" s="1"/>
     </row>
-    <row r="4" spans="1:44" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:51" x14ac:dyDescent="0.35">
       <c r="A4" s="1">
         <v>45172</v>
       </c>
@@ -670,7 +712,7 @@
       <c r="G4" s="1"/>
       <c r="H4" s="1"/>
     </row>
-    <row r="5" spans="1:44" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:51" x14ac:dyDescent="0.35">
       <c r="A5" s="1">
         <v>45173</v>
       </c>
@@ -682,7 +724,7 @@
       <c r="G5" s="1"/>
       <c r="H5" s="1"/>
     </row>
-    <row r="6" spans="1:44" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:51" x14ac:dyDescent="0.35">
       <c r="A6" s="1">
         <v>45174</v>
       </c>
@@ -694,7 +736,7 @@
       <c r="G6" s="1"/>
       <c r="H6" s="1"/>
     </row>
-    <row r="7" spans="1:44" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:51" x14ac:dyDescent="0.35">
       <c r="A7" s="1">
         <v>45175</v>
       </c>
@@ -706,7 +748,7 @@
       <c r="G7" s="1"/>
       <c r="H7" s="1"/>
     </row>
-    <row r="8" spans="1:44" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:51" x14ac:dyDescent="0.35">
       <c r="A8" s="1">
         <v>45176</v>
       </c>
@@ -720,7 +762,7 @@
       <c r="G8" s="1"/>
       <c r="H8" s="1"/>
     </row>
-    <row r="9" spans="1:44" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:51" x14ac:dyDescent="0.35">
       <c r="A9" s="1">
         <v>45177</v>
       </c>
@@ -732,7 +774,7 @@
       <c r="G9" s="1"/>
       <c r="H9" s="1"/>
     </row>
-    <row r="10" spans="1:44" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:51" x14ac:dyDescent="0.35">
       <c r="A10" s="1">
         <v>45178</v>
       </c>
@@ -744,7 +786,7 @@
       <c r="G10" s="1"/>
       <c r="H10" s="1"/>
     </row>
-    <row r="11" spans="1:44" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:51" x14ac:dyDescent="0.35">
       <c r="A11" s="1">
         <v>45179</v>
       </c>
@@ -756,7 +798,7 @@
       <c r="G11" s="1"/>
       <c r="H11" s="1"/>
     </row>
-    <row r="12" spans="1:44" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:51" x14ac:dyDescent="0.35">
       <c r="A12" s="1">
         <v>45180</v>
       </c>
@@ -768,7 +810,7 @@
       <c r="G12" s="1"/>
       <c r="H12" s="1"/>
     </row>
-    <row r="13" spans="1:44" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:51" x14ac:dyDescent="0.35">
       <c r="A13" s="1">
         <v>45181</v>
       </c>
@@ -780,7 +822,7 @@
       <c r="G13" s="1"/>
       <c r="H13" s="1"/>
     </row>
-    <row r="14" spans="1:44" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:51" x14ac:dyDescent="0.35">
       <c r="A14" s="1">
         <v>45182</v>
       </c>
@@ -792,7 +834,7 @@
       <c r="G14" s="1"/>
       <c r="H14" s="1"/>
     </row>
-    <row r="15" spans="1:44" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:51" x14ac:dyDescent="0.35">
       <c r="A15" s="1">
         <v>45183</v>
       </c>
@@ -804,7 +846,7 @@
       <c r="G15" s="1"/>
       <c r="H15" s="1"/>
     </row>
-    <row r="16" spans="1:44" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:51" x14ac:dyDescent="0.35">
       <c r="A16" s="1">
         <v>45184</v>
       </c>
@@ -2574,7 +2616,7 @@
       <c r="Y112" s="3"/>
       <c r="Z112" s="3"/>
     </row>
-    <row r="113" spans="1:44" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:51" x14ac:dyDescent="0.35">
       <c r="A113" s="1">
         <v>45281</v>
       </c>
@@ -2604,7 +2646,7 @@
       <c r="Y113" s="3"/>
       <c r="Z113" s="3"/>
     </row>
-    <row r="114" spans="1:44" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:51" x14ac:dyDescent="0.35">
       <c r="A114" s="1">
         <v>45282</v>
       </c>
@@ -2634,7 +2676,7 @@
       <c r="Y114" s="3"/>
       <c r="Z114" s="3"/>
     </row>
-    <row r="115" spans="1:44" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:51" x14ac:dyDescent="0.35">
       <c r="A115" s="1">
         <v>45283</v>
       </c>
@@ -2664,7 +2706,7 @@
       <c r="Y115" s="3"/>
       <c r="Z115" s="3"/>
     </row>
-    <row r="116" spans="1:44" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:51" x14ac:dyDescent="0.35">
       <c r="A116" s="1">
         <v>45284</v>
       </c>
@@ -2694,7 +2736,7 @@
       <c r="Y116" s="3"/>
       <c r="Z116" s="3"/>
     </row>
-    <row r="117" spans="1:44" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:51" x14ac:dyDescent="0.35">
       <c r="A117" s="1">
         <v>45285</v>
       </c>
@@ -2723,8 +2765,11 @@
       <c r="X117" s="3"/>
       <c r="Y117" s="3"/>
       <c r="Z117" s="3"/>
-    </row>
-    <row r="118" spans="1:44" x14ac:dyDescent="0.35">
+      <c r="AS117">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="118" spans="1:51" x14ac:dyDescent="0.35">
       <c r="A118" s="1">
         <v>45286</v>
       </c>
@@ -2753,8 +2798,11 @@
       <c r="X118" s="3"/>
       <c r="Y118" s="3"/>
       <c r="Z118" s="3"/>
-    </row>
-    <row r="119" spans="1:44" x14ac:dyDescent="0.35">
+      <c r="AT118">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="119" spans="1:51" x14ac:dyDescent="0.35">
       <c r="A119" s="1">
         <v>45287</v>
       </c>
@@ -2783,8 +2831,11 @@
       <c r="X119" s="3"/>
       <c r="Y119" s="3"/>
       <c r="Z119" s="3"/>
-    </row>
-    <row r="120" spans="1:44" x14ac:dyDescent="0.35">
+      <c r="AU119">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="120" spans="1:51" x14ac:dyDescent="0.35">
       <c r="A120" s="1">
         <v>45288</v>
       </c>
@@ -2813,8 +2864,11 @@
       <c r="X120" s="3"/>
       <c r="Y120" s="3"/>
       <c r="Z120" s="3"/>
-    </row>
-    <row r="121" spans="1:44" x14ac:dyDescent="0.35">
+      <c r="AV120">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="121" spans="1:51" x14ac:dyDescent="0.35">
       <c r="A121" s="1">
         <v>45289</v>
       </c>
@@ -2843,8 +2897,11 @@
       <c r="X121" s="3"/>
       <c r="Y121" s="3"/>
       <c r="Z121" s="3"/>
-    </row>
-    <row r="122" spans="1:44" x14ac:dyDescent="0.35">
+      <c r="AW121">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="122" spans="1:51" x14ac:dyDescent="0.35">
       <c r="A122" s="1">
         <v>45290</v>
       </c>
@@ -2873,8 +2930,11 @@
       <c r="X122" s="3"/>
       <c r="Y122" s="3"/>
       <c r="Z122" s="3"/>
-    </row>
-    <row r="123" spans="1:44" x14ac:dyDescent="0.35">
+      <c r="AX122">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="123" spans="1:51" x14ac:dyDescent="0.35">
       <c r="A123" s="1">
         <v>45291</v>
       </c>
@@ -2903,8 +2963,11 @@
       <c r="X123" s="3"/>
       <c r="Y123" s="3"/>
       <c r="Z123" s="3"/>
-    </row>
-    <row r="124" spans="1:44" x14ac:dyDescent="0.35">
+      <c r="AY123">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="124" spans="1:51" x14ac:dyDescent="0.35">
       <c r="A124" s="1">
         <v>45536</v>
       </c>
@@ -2951,7 +3014,7 @@
       <c r="AQ124" s="2"/>
       <c r="AR124" s="2"/>
     </row>
-    <row r="125" spans="1:44" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:51" x14ac:dyDescent="0.35">
       <c r="A125" s="1">
         <v>45537</v>
       </c>
@@ -2998,7 +3061,7 @@
       <c r="AQ125" s="2"/>
       <c r="AR125" s="2"/>
     </row>
-    <row r="126" spans="1:44" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:51" x14ac:dyDescent="0.35">
       <c r="A126" s="1">
         <v>45538</v>
       </c>
@@ -3045,7 +3108,7 @@
       <c r="AQ126" s="2"/>
       <c r="AR126" s="2"/>
     </row>
-    <row r="127" spans="1:44" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:51" x14ac:dyDescent="0.35">
       <c r="A127" s="1">
         <v>45539</v>
       </c>
@@ -3092,7 +3155,7 @@
       <c r="AQ127" s="2"/>
       <c r="AR127" s="2"/>
     </row>
-    <row r="128" spans="1:44" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:51" x14ac:dyDescent="0.35">
       <c r="A128" s="1">
         <v>45540</v>
       </c>
@@ -7766,7 +7829,7 @@
       <c r="AQ224" s="2"/>
       <c r="AR224" s="2"/>
     </row>
-    <row r="225" spans="1:44" x14ac:dyDescent="0.35">
+    <row r="225" spans="1:46" x14ac:dyDescent="0.35">
       <c r="A225" s="1">
         <v>45637</v>
       </c>
@@ -7813,7 +7876,7 @@
       <c r="AQ225" s="2"/>
       <c r="AR225" s="2"/>
     </row>
-    <row r="226" spans="1:44" x14ac:dyDescent="0.35">
+    <row r="226" spans="1:46" x14ac:dyDescent="0.35">
       <c r="A226" s="1">
         <v>45638</v>
       </c>
@@ -7860,7 +7923,7 @@
       <c r="AQ226" s="2"/>
       <c r="AR226" s="2"/>
     </row>
-    <row r="227" spans="1:44" x14ac:dyDescent="0.35">
+    <row r="227" spans="1:46" x14ac:dyDescent="0.35">
       <c r="A227" s="1">
         <v>45639</v>
       </c>
@@ -7907,7 +7970,7 @@
       <c r="AQ227" s="2"/>
       <c r="AR227" s="2"/>
     </row>
-    <row r="228" spans="1:44" x14ac:dyDescent="0.35">
+    <row r="228" spans="1:46" x14ac:dyDescent="0.35">
       <c r="A228" s="1">
         <v>45640</v>
       </c>
@@ -7954,7 +8017,7 @@
       <c r="AQ228" s="2"/>
       <c r="AR228" s="2"/>
     </row>
-    <row r="229" spans="1:44" x14ac:dyDescent="0.35">
+    <row r="229" spans="1:46" x14ac:dyDescent="0.35">
       <c r="A229" s="1">
         <v>45641</v>
       </c>
@@ -8001,7 +8064,7 @@
       <c r="AQ229" s="2"/>
       <c r="AR229" s="2"/>
     </row>
-    <row r="230" spans="1:44" x14ac:dyDescent="0.35">
+    <row r="230" spans="1:46" x14ac:dyDescent="0.35">
       <c r="A230" s="1">
         <v>45642</v>
       </c>
@@ -8048,7 +8111,7 @@
       <c r="AQ230" s="2"/>
       <c r="AR230" s="2"/>
     </row>
-    <row r="231" spans="1:44" x14ac:dyDescent="0.35">
+    <row r="231" spans="1:46" x14ac:dyDescent="0.35">
       <c r="A231" s="1">
         <v>45643</v>
       </c>
@@ -8095,7 +8158,7 @@
       <c r="AQ231" s="2"/>
       <c r="AR231" s="2"/>
     </row>
-    <row r="232" spans="1:44" x14ac:dyDescent="0.35">
+    <row r="232" spans="1:46" x14ac:dyDescent="0.35">
       <c r="A232" s="1">
         <v>45644</v>
       </c>
@@ -8142,7 +8205,7 @@
       <c r="AQ232" s="2"/>
       <c r="AR232" s="2"/>
     </row>
-    <row r="233" spans="1:44" x14ac:dyDescent="0.35">
+    <row r="233" spans="1:46" x14ac:dyDescent="0.35">
       <c r="A233" s="1">
         <v>45645</v>
       </c>
@@ -8189,7 +8252,7 @@
       <c r="AQ233" s="2"/>
       <c r="AR233" s="2"/>
     </row>
-    <row r="234" spans="1:44" x14ac:dyDescent="0.35">
+    <row r="234" spans="1:46" x14ac:dyDescent="0.35">
       <c r="A234" s="1">
         <v>45646</v>
       </c>
@@ -8236,7 +8299,7 @@
       <c r="AQ234" s="2"/>
       <c r="AR234" s="2"/>
     </row>
-    <row r="235" spans="1:44" x14ac:dyDescent="0.35">
+    <row r="235" spans="1:46" x14ac:dyDescent="0.35">
       <c r="A235" s="1">
         <v>45647</v>
       </c>
@@ -8283,7 +8346,7 @@
       <c r="AQ235" s="2"/>
       <c r="AR235" s="2"/>
     </row>
-    <row r="236" spans="1:44" x14ac:dyDescent="0.35">
+    <row r="236" spans="1:46" x14ac:dyDescent="0.35">
       <c r="A236" s="1">
         <v>45648</v>
       </c>
@@ -8330,7 +8393,7 @@
       <c r="AQ236" s="2"/>
       <c r="AR236" s="2"/>
     </row>
-    <row r="237" spans="1:44" x14ac:dyDescent="0.35">
+    <row r="237" spans="1:46" x14ac:dyDescent="0.35">
       <c r="A237" s="1">
         <v>45649</v>
       </c>
@@ -8377,7 +8440,7 @@
       <c r="AQ237" s="2"/>
       <c r="AR237" s="2"/>
     </row>
-    <row r="238" spans="1:44" x14ac:dyDescent="0.35">
+    <row r="238" spans="1:46" x14ac:dyDescent="0.35">
       <c r="A238" s="1">
         <v>45650</v>
       </c>
@@ -8424,7 +8487,7 @@
       <c r="AQ238" s="2"/>
       <c r="AR238" s="2"/>
     </row>
-    <row r="239" spans="1:44" x14ac:dyDescent="0.35">
+    <row r="239" spans="1:46" x14ac:dyDescent="0.35">
       <c r="A239" s="1">
         <v>45651</v>
       </c>
@@ -8470,8 +8533,11 @@
       <c r="AP239" s="2"/>
       <c r="AQ239" s="2"/>
       <c r="AR239" s="2"/>
-    </row>
-    <row r="240" spans="1:44" x14ac:dyDescent="0.35">
+      <c r="AS239">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="240" spans="1:46" x14ac:dyDescent="0.35">
       <c r="A240" s="1">
         <v>45652</v>
       </c>
@@ -8517,8 +8583,11 @@
       <c r="AP240" s="2"/>
       <c r="AQ240" s="2"/>
       <c r="AR240" s="2"/>
-    </row>
-    <row r="241" spans="1:44" x14ac:dyDescent="0.35">
+      <c r="AT240">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="241" spans="1:51" x14ac:dyDescent="0.35">
       <c r="A241" s="1">
         <v>45653</v>
       </c>
@@ -8564,8 +8633,11 @@
       <c r="AP241" s="2"/>
       <c r="AQ241" s="2"/>
       <c r="AR241" s="2"/>
-    </row>
-    <row r="242" spans="1:44" x14ac:dyDescent="0.35">
+      <c r="AU241">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="242" spans="1:51" x14ac:dyDescent="0.35">
       <c r="A242" s="1">
         <v>45654</v>
       </c>
@@ -8611,8 +8683,11 @@
       <c r="AP242" s="2"/>
       <c r="AQ242" s="2"/>
       <c r="AR242" s="2"/>
-    </row>
-    <row r="243" spans="1:44" x14ac:dyDescent="0.35">
+      <c r="AV242">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="243" spans="1:51" x14ac:dyDescent="0.35">
       <c r="A243" s="1">
         <v>45655</v>
       </c>
@@ -8658,8 +8733,11 @@
       <c r="AP243" s="2"/>
       <c r="AQ243" s="2"/>
       <c r="AR243" s="2"/>
-    </row>
-    <row r="244" spans="1:44" x14ac:dyDescent="0.35">
+      <c r="AW243">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="244" spans="1:51" x14ac:dyDescent="0.35">
       <c r="A244" s="1">
         <v>45656</v>
       </c>
@@ -8705,8 +8783,11 @@
       <c r="AP244" s="2"/>
       <c r="AQ244" s="2"/>
       <c r="AR244" s="2"/>
-    </row>
-    <row r="245" spans="1:44" x14ac:dyDescent="0.35">
+      <c r="AX244">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="245" spans="1:51" x14ac:dyDescent="0.35">
       <c r="A245" s="1">
         <v>45657</v>
       </c>
@@ -8752,8 +8833,11 @@
       <c r="AP245" s="2"/>
       <c r="AQ245" s="2"/>
       <c r="AR245" s="2"/>
-    </row>
-    <row r="246" spans="1:44" x14ac:dyDescent="0.35">
+      <c r="AY245">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="246" spans="1:51" x14ac:dyDescent="0.35">
       <c r="A246" s="1">
         <v>45901</v>
       </c>
@@ -8800,7 +8884,7 @@
       <c r="AQ246" s="2"/>
       <c r="AR246" s="2"/>
     </row>
-    <row r="247" spans="1:44" x14ac:dyDescent="0.35">
+    <row r="247" spans="1:51" x14ac:dyDescent="0.35">
       <c r="A247" s="1">
         <v>45902</v>
       </c>
@@ -8847,7 +8931,7 @@
       <c r="AQ247" s="2"/>
       <c r="AR247" s="2"/>
     </row>
-    <row r="248" spans="1:44" x14ac:dyDescent="0.35">
+    <row r="248" spans="1:51" x14ac:dyDescent="0.35">
       <c r="A248" s="1">
         <v>45903</v>
       </c>
@@ -8894,7 +8978,7 @@
       <c r="AQ248" s="2"/>
       <c r="AR248" s="2"/>
     </row>
-    <row r="249" spans="1:44" x14ac:dyDescent="0.35">
+    <row r="249" spans="1:51" x14ac:dyDescent="0.35">
       <c r="A249" s="1">
         <v>45904</v>
       </c>
@@ -8941,7 +9025,7 @@
       <c r="AQ249" s="2"/>
       <c r="AR249" s="2"/>
     </row>
-    <row r="250" spans="1:44" x14ac:dyDescent="0.35">
+    <row r="250" spans="1:51" x14ac:dyDescent="0.35">
       <c r="A250" s="1">
         <v>45905</v>
       </c>
@@ -8990,7 +9074,7 @@
       <c r="AQ250" s="2"/>
       <c r="AR250" s="2"/>
     </row>
-    <row r="251" spans="1:44" x14ac:dyDescent="0.35">
+    <row r="251" spans="1:51" x14ac:dyDescent="0.35">
       <c r="A251" s="1">
         <v>45906</v>
       </c>
@@ -9037,7 +9121,7 @@
       <c r="AQ251" s="2"/>
       <c r="AR251" s="2"/>
     </row>
-    <row r="252" spans="1:44" x14ac:dyDescent="0.35">
+    <row r="252" spans="1:51" x14ac:dyDescent="0.35">
       <c r="A252" s="1">
         <v>45907</v>
       </c>
@@ -9087,7 +9171,7 @@
       <c r="AQ252" s="2"/>
       <c r="AR252" s="2"/>
     </row>
-    <row r="253" spans="1:44" x14ac:dyDescent="0.35">
+    <row r="253" spans="1:51" x14ac:dyDescent="0.35">
       <c r="A253" s="1">
         <v>45908</v>
       </c>
@@ -9136,7 +9220,7 @@
       <c r="AQ253" s="2"/>
       <c r="AR253" s="2"/>
     </row>
-    <row r="254" spans="1:44" x14ac:dyDescent="0.35">
+    <row r="254" spans="1:51" x14ac:dyDescent="0.35">
       <c r="A254" s="1">
         <v>45909</v>
       </c>
@@ -9185,7 +9269,7 @@
       <c r="AQ254" s="2"/>
       <c r="AR254" s="2"/>
     </row>
-    <row r="255" spans="1:44" x14ac:dyDescent="0.35">
+    <row r="255" spans="1:51" x14ac:dyDescent="0.35">
       <c r="A255" s="1">
         <v>45910</v>
       </c>
@@ -9234,7 +9318,7 @@
       <c r="AQ255" s="2"/>
       <c r="AR255" s="2"/>
     </row>
-    <row r="256" spans="1:44" x14ac:dyDescent="0.35">
+    <row r="256" spans="1:51" x14ac:dyDescent="0.35">
       <c r="A256" s="1">
         <v>45911</v>
       </c>
@@ -13907,7 +13991,7 @@
       <c r="AQ352" s="2"/>
       <c r="AR352" s="2"/>
     </row>
-    <row r="353" spans="1:44" x14ac:dyDescent="0.35">
+    <row r="353" spans="1:51" x14ac:dyDescent="0.35">
       <c r="A353" s="1">
         <v>46008</v>
       </c>
@@ -13954,7 +14038,7 @@
       <c r="AQ353" s="2"/>
       <c r="AR353" s="2"/>
     </row>
-    <row r="354" spans="1:44" x14ac:dyDescent="0.35">
+    <row r="354" spans="1:51" x14ac:dyDescent="0.35">
       <c r="A354" s="1">
         <v>46009</v>
       </c>
@@ -14001,7 +14085,7 @@
       <c r="AQ354" s="2"/>
       <c r="AR354" s="2"/>
     </row>
-    <row r="355" spans="1:44" x14ac:dyDescent="0.35">
+    <row r="355" spans="1:51" x14ac:dyDescent="0.35">
       <c r="A355" s="1">
         <v>46010</v>
       </c>
@@ -14048,7 +14132,7 @@
       <c r="AQ355" s="2"/>
       <c r="AR355" s="2"/>
     </row>
-    <row r="356" spans="1:44" x14ac:dyDescent="0.35">
+    <row r="356" spans="1:51" x14ac:dyDescent="0.35">
       <c r="A356" s="1">
         <v>46011</v>
       </c>
@@ -14095,7 +14179,7 @@
       <c r="AQ356" s="2"/>
       <c r="AR356" s="2"/>
     </row>
-    <row r="357" spans="1:44" x14ac:dyDescent="0.35">
+    <row r="357" spans="1:51" x14ac:dyDescent="0.35">
       <c r="A357" s="1">
         <v>46012</v>
       </c>
@@ -14142,7 +14226,7 @@
       <c r="AQ357" s="2"/>
       <c r="AR357" s="2"/>
     </row>
-    <row r="358" spans="1:44" x14ac:dyDescent="0.35">
+    <row r="358" spans="1:51" x14ac:dyDescent="0.35">
       <c r="A358" s="1">
         <v>46013</v>
       </c>
@@ -14189,7 +14273,7 @@
       <c r="AQ358" s="2"/>
       <c r="AR358" s="2"/>
     </row>
-    <row r="359" spans="1:44" x14ac:dyDescent="0.35">
+    <row r="359" spans="1:51" x14ac:dyDescent="0.35">
       <c r="A359" s="1">
         <v>46014</v>
       </c>
@@ -14236,7 +14320,7 @@
       <c r="AQ359" s="2"/>
       <c r="AR359" s="2"/>
     </row>
-    <row r="360" spans="1:44" x14ac:dyDescent="0.35">
+    <row r="360" spans="1:51" x14ac:dyDescent="0.35">
       <c r="A360" s="1">
         <v>46015</v>
       </c>
@@ -14283,7 +14367,7 @@
       <c r="AQ360" s="2"/>
       <c r="AR360" s="2"/>
     </row>
-    <row r="361" spans="1:44" x14ac:dyDescent="0.35">
+    <row r="361" spans="1:51" x14ac:dyDescent="0.35">
       <c r="A361" s="1">
         <v>46016</v>
       </c>
@@ -14329,8 +14413,11 @@
       <c r="AP361" s="2"/>
       <c r="AQ361" s="2"/>
       <c r="AR361" s="2"/>
-    </row>
-    <row r="362" spans="1:44" x14ac:dyDescent="0.35">
+      <c r="AS361">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="362" spans="1:51" x14ac:dyDescent="0.35">
       <c r="A362" s="1">
         <v>46017</v>
       </c>
@@ -14376,8 +14463,11 @@
       <c r="AP362" s="2"/>
       <c r="AQ362" s="2"/>
       <c r="AR362" s="2"/>
-    </row>
-    <row r="363" spans="1:44" x14ac:dyDescent="0.35">
+      <c r="AT362">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="363" spans="1:51" x14ac:dyDescent="0.35">
       <c r="A363" s="1">
         <v>46018</v>
       </c>
@@ -14423,8 +14513,11 @@
       <c r="AP363" s="2"/>
       <c r="AQ363" s="2"/>
       <c r="AR363" s="2"/>
-    </row>
-    <row r="364" spans="1:44" x14ac:dyDescent="0.35">
+      <c r="AU363">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="364" spans="1:51" x14ac:dyDescent="0.35">
       <c r="A364" s="1">
         <v>46019</v>
       </c>
@@ -14470,8 +14563,11 @@
       <c r="AP364" s="2"/>
       <c r="AQ364" s="2"/>
       <c r="AR364" s="2"/>
-    </row>
-    <row r="365" spans="1:44" x14ac:dyDescent="0.35">
+      <c r="AV364">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="365" spans="1:51" x14ac:dyDescent="0.35">
       <c r="A365" s="1">
         <v>46020</v>
       </c>
@@ -14517,8 +14613,11 @@
       <c r="AP365" s="2"/>
       <c r="AQ365" s="2"/>
       <c r="AR365" s="2"/>
-    </row>
-    <row r="366" spans="1:44" x14ac:dyDescent="0.35">
+      <c r="AW365">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="366" spans="1:51" x14ac:dyDescent="0.35">
       <c r="A366" s="1">
         <v>46021</v>
       </c>
@@ -14564,8 +14663,11 @@
       <c r="AP366" s="2"/>
       <c r="AQ366" s="2"/>
       <c r="AR366" s="2"/>
-    </row>
-    <row r="367" spans="1:44" x14ac:dyDescent="0.35">
+      <c r="AX366">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="367" spans="1:51" x14ac:dyDescent="0.35">
       <c r="A367" s="1">
         <v>46022</v>
       </c>
@@ -14611,8 +14713,11 @@
       <c r="AP367" s="2"/>
       <c r="AQ367" s="2"/>
       <c r="AR367" s="2"/>
-    </row>
-    <row r="368" spans="1:44" x14ac:dyDescent="0.35">
+      <c r="AY367">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="368" spans="1:51" x14ac:dyDescent="0.35">
       <c r="B368" s="2"/>
       <c r="C368" s="2"/>
       <c r="D368" s="2"/>
